--- a/zy72341/data/demo_answers.xlsx
+++ b/zy72341/data/demo_answers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>answer_id</t>
   </si>
@@ -52,6 +52,12 @@
     <t>A004</t>
   </si>
   <si>
+    <t>A005</t>
+  </si>
+  <si>
+    <t>A006</t>
+  </si>
+  <si>
     <t>S001</t>
   </si>
   <si>
@@ -61,6 +67,12 @@
     <t>S003</t>
   </si>
   <si>
+    <t>S004</t>
+  </si>
+  <si>
+    <t>S005</t>
+  </si>
+  <si>
     <t>张三</t>
   </si>
   <si>
@@ -70,22 +82,37 @@
     <t>王五</t>
   </si>
   <si>
+    <t>赵六</t>
+  </si>
+  <si>
+    <t>孙七</t>
+  </si>
+  <si>
     <t>Q1</t>
   </si>
   <si>
     <t>Q2</t>
   </si>
   <si>
-    <t>这是一个完整的答案内容...</t>
-  </si>
-  <si>
-    <t>第一版答案内容...</t>
-  </si>
-  <si>
-    <t>第二版修改后的答案...</t>
-  </si>
-  <si>
-    <t>旧口径下的答案...</t>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>这是一份完整的答题内容，结构清晰、论证充分、符合评分标准所有要点。</t>
+  </si>
+  <si>
+    <t>第一版初步作答，部分要点未展开论述完整。</t>
+  </si>
+  <si>
+    <t>第二版补充修改后完整作答，补充了缺失要点、调整了论述逻辑，比第一版更完整。</t>
+  </si>
+  <si>
+    <t>旧评分标准下的作答，在当时标准下得分较高，但在新标准中权重需要调整。</t>
+  </si>
+  <si>
+    <t>满分</t>
+  </si>
+  <si>
+    <t>基本答出了及格线附近的要点，部分论述稍显薄弱。</t>
   </si>
   <si>
     <t>2024-01-15 10:30:00</t>
@@ -100,16 +127,28 @@
     <t>2024-01-10 09:00:00</t>
   </si>
   <si>
-    <t>顺利记录，无异常</t>
-  </si>
-  <si>
-    <t>同一学生提交两版答案</t>
-  </si>
-  <si>
-    <t>重交版答案</t>
-  </si>
-  <si>
-    <t>后续将从评分权重表补录</t>
+    <t>2024-01-16 15:20:00</t>
+  </si>
+  <si>
+    <t>2024-01-16 16:45:00</t>
+  </si>
+  <si>
+    <t>顺利记录样例：答题正常、评分正常，无任何异常</t>
+  </si>
+  <si>
+    <t>重复答案样例：同一学生两版答案（第1版）</t>
+  </si>
+  <si>
+    <t>重复答案样例：同一学生两版答案（第2版重交版）</t>
+  </si>
+  <si>
+    <t>旧口径样例：后续将由运营规划阿岚补看评分权重表后补录误差说明</t>
+  </si>
+  <si>
+    <t>边界值样例：满分触发边界检查，答案内容过短也需告警（实际内容丰富度与得分不匹配）</t>
+  </si>
+  <si>
+    <t>边界值样例：及格线附近（60分），建议复核评分公允性</t>
   </si>
 </sst>
 </file>
@@ -467,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -501,25 +540,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>85</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -527,25 +566,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>78</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -553,25 +592,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -579,25 +618,77 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>92</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>60</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
